--- a/artfynd/A 44936-2025 artfynd.xlsx
+++ b/artfynd/A 44936-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129478200</v>
+        <v>129495314</v>
       </c>
       <c r="B2" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407203</v>
+        <v>407305</v>
       </c>
       <c r="R2" t="n">
-        <v>6823039</v>
+        <v>6822639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129478209</v>
+        <v>129495309</v>
       </c>
       <c r="B3" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407521</v>
+        <v>407320</v>
       </c>
       <c r="R3" t="n">
-        <v>6822449</v>
+        <v>6822525</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129495182</v>
+        <v>129478308</v>
       </c>
       <c r="B4" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407173</v>
+        <v>407271</v>
       </c>
       <c r="R4" t="n">
-        <v>6823280</v>
+        <v>6822740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129495273</v>
+        <v>129495243</v>
       </c>
       <c r="B5" t="n">
-        <v>78834</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407323</v>
+        <v>407360</v>
       </c>
       <c r="R5" t="n">
-        <v>6822521</v>
+        <v>6822661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129495264</v>
+        <v>129478200</v>
       </c>
       <c r="B6" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407464</v>
+        <v>407203</v>
       </c>
       <c r="R6" t="n">
-        <v>6822329</v>
+        <v>6823039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1156,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129495218</v>
+        <v>129478209</v>
       </c>
       <c r="B7" t="n">
-        <v>79666</v>
+        <v>79695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407405</v>
+        <v>407521</v>
       </c>
       <c r="R7" t="n">
-        <v>6822602</v>
+        <v>6822449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1253,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129495256</v>
+        <v>129495182</v>
       </c>
       <c r="B8" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1276,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407292</v>
+        <v>407173</v>
       </c>
       <c r="R8" t="n">
-        <v>6823105</v>
+        <v>6823280</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,7 +1344,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1358,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129495314</v>
+        <v>129495273</v>
       </c>
       <c r="B9" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1369,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1393,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407305</v>
+        <v>407323</v>
       </c>
       <c r="R9" t="n">
-        <v>6822639</v>
+        <v>6822521</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129495309</v>
+        <v>129495264</v>
       </c>
       <c r="B10" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1466,21 +1470,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407320</v>
+        <v>407464</v>
       </c>
       <c r="R10" t="n">
-        <v>6822525</v>
+        <v>6822329</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129478308</v>
+        <v>129495218</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1563,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407271</v>
+        <v>407405</v>
       </c>
       <c r="R11" t="n">
-        <v>6822740</v>
+        <v>6822602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1637,22 +1641,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129495243</v>
+        <v>129495256</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>78834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1660,31 +1664,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1692,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407360</v>
+        <v>407292</v>
       </c>
       <c r="R12" t="n">
-        <v>6822661</v>
+        <v>6823105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1735,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129495308</v>
+        <v>129495291</v>
       </c>
       <c r="B51" t="n">
         <v>78833</v>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407326</v>
+        <v>407457</v>
       </c>
       <c r="R51" t="n">
-        <v>6822521</v>
+        <v>6822425</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5585,10 +5585,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129495291</v>
+        <v>129478300</v>
       </c>
       <c r="B52" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5596,21 +5596,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>407457</v>
+        <v>407468</v>
       </c>
       <c r="R52" t="n">
-        <v>6822425</v>
+        <v>6822633</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5670,22 +5670,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129478300</v>
+        <v>129495286</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5693,21 +5693,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5717,10 +5717,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407468</v>
+        <v>407274</v>
       </c>
       <c r="R53" t="n">
-        <v>6822633</v>
+        <v>6823142</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5767,22 +5767,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129495286</v>
+        <v>129478302</v>
       </c>
       <c r="B54" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5790,21 +5790,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407274</v>
+        <v>407408</v>
       </c>
       <c r="R54" t="n">
-        <v>6823142</v>
+        <v>6822212</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5864,22 +5864,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129478302</v>
+        <v>129478281</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5887,21 +5887,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407408</v>
+        <v>407417</v>
       </c>
       <c r="R55" t="n">
-        <v>6822212</v>
+        <v>6822269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5973,10 +5973,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129478281</v>
+        <v>129478298</v>
       </c>
       <c r="B56" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5984,21 +5984,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407417</v>
+        <v>407339</v>
       </c>
       <c r="R56" t="n">
-        <v>6822269</v>
+        <v>6822779</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6044,6 +6044,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6070,7 +6075,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129478298</v>
+        <v>129478305</v>
       </c>
       <c r="B57" t="n">
         <v>79076</v>
@@ -6105,10 +6110,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407339</v>
+        <v>407395</v>
       </c>
       <c r="R57" t="n">
-        <v>6822779</v>
+        <v>6822461</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6141,11 +6146,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6172,10 +6172,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129478305</v>
+        <v>129495285</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6183,21 +6183,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407395</v>
+        <v>407222</v>
       </c>
       <c r="R58" t="n">
-        <v>6822461</v>
+        <v>6823145</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6257,22 +6257,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129495285</v>
+        <v>129495194</v>
       </c>
       <c r="B59" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6280,21 +6280,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407222</v>
+        <v>407452</v>
       </c>
       <c r="R59" t="n">
-        <v>6823145</v>
+        <v>6822376</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129495194</v>
+        <v>129495308</v>
       </c>
       <c r="B60" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6377,21 +6377,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407452</v>
+        <v>407326</v>
       </c>
       <c r="R60" t="n">
-        <v>6822376</v>
+        <v>6822521</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -9203,10 +9203,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129495341</v>
+        <v>129478252</v>
       </c>
       <c r="B89" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9214,21 +9214,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9238,10 +9238,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407305</v>
+        <v>407320</v>
       </c>
       <c r="R89" t="n">
-        <v>6822819</v>
+        <v>6823016</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9288,22 +9288,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129495371</v>
+        <v>129495266</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9311,21 +9311,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407244</v>
+        <v>407345</v>
       </c>
       <c r="R90" t="n">
-        <v>6822729</v>
+        <v>6822265</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9397,10 +9397,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129478276</v>
+        <v>129495222</v>
       </c>
       <c r="B91" t="n">
-        <v>78833</v>
+        <v>79666</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9408,21 +9408,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9432,10 +9432,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407535</v>
+        <v>407454</v>
       </c>
       <c r="R91" t="n">
-        <v>6822520</v>
+        <v>6822397</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9482,19 +9482,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129495359</v>
+        <v>129495341</v>
       </c>
       <c r="B92" t="n">
         <v>79076</v>
@@ -9523,19 +9523,16 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407400</v>
+        <v>407305</v>
       </c>
       <c r="R92" t="n">
-        <v>6822209</v>
+        <v>6822819</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9576,7 +9573,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9595,7 +9591,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129495336</v>
+        <v>129495371</v>
       </c>
       <c r="B93" t="n">
         <v>79076</v>
@@ -9630,10 +9626,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407088</v>
+        <v>407244</v>
       </c>
       <c r="R93" t="n">
-        <v>6823461</v>
+        <v>6822729</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9692,10 +9688,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129495169</v>
+        <v>129478276</v>
       </c>
       <c r="B94" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9703,21 +9699,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9727,10 +9723,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407109</v>
+        <v>407535</v>
       </c>
       <c r="R94" t="n">
-        <v>6823069</v>
+        <v>6822520</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9777,22 +9773,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129495210</v>
+        <v>129495359</v>
       </c>
       <c r="B95" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9800,34 +9796,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407328</v>
+        <v>407400</v>
       </c>
       <c r="R95" t="n">
-        <v>6822512</v>
+        <v>6822209</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9868,6 +9867,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9886,10 +9886,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129495183</v>
+        <v>129495336</v>
       </c>
       <c r="B96" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407209</v>
+        <v>407088</v>
       </c>
       <c r="R96" t="n">
-        <v>6823207</v>
+        <v>6823461</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9983,7 +9983,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129495187</v>
+        <v>129495169</v>
       </c>
       <c r="B97" t="n">
         <v>79695</v>
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407280</v>
+        <v>407109</v>
       </c>
       <c r="R97" t="n">
-        <v>6822879</v>
+        <v>6823069</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10080,7 +10080,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129478202</v>
+        <v>129495210</v>
       </c>
       <c r="B98" t="n">
         <v>79695</v>
@@ -10115,10 +10115,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407245</v>
+        <v>407328</v>
       </c>
       <c r="R98" t="n">
-        <v>6823196</v>
+        <v>6822512</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10165,19 +10165,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129495177</v>
+        <v>129495183</v>
       </c>
       <c r="B99" t="n">
         <v>79695</v>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407097</v>
+        <v>407209</v>
       </c>
       <c r="R99" t="n">
-        <v>6823458</v>
+        <v>6823207</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10274,7 +10274,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129495199</v>
+        <v>129495187</v>
       </c>
       <c r="B100" t="n">
         <v>79695</v>
@@ -10309,10 +10309,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407337</v>
+        <v>407280</v>
       </c>
       <c r="R100" t="n">
-        <v>6822261</v>
+        <v>6822879</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10371,7 +10371,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129478213</v>
+        <v>129478202</v>
       </c>
       <c r="B101" t="n">
         <v>79695</v>
@@ -10406,10 +10406,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407414</v>
+        <v>407245</v>
       </c>
       <c r="R101" t="n">
-        <v>6822268</v>
+        <v>6823196</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10468,7 +10468,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129478223</v>
+        <v>129495177</v>
       </c>
       <c r="B102" t="n">
         <v>79695</v>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>407383</v>
+        <v>407097</v>
       </c>
       <c r="R102" t="n">
-        <v>6822530</v>
+        <v>6823458</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10553,22 +10553,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129478252</v>
+        <v>129495199</v>
       </c>
       <c r="B103" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10576,21 +10576,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10600,10 +10600,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407320</v>
+        <v>407337</v>
       </c>
       <c r="R103" t="n">
-        <v>6823016</v>
+        <v>6822261</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10650,22 +10650,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129495266</v>
+        <v>129478213</v>
       </c>
       <c r="B104" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10673,21 +10673,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10697,10 +10697,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407345</v>
+        <v>407414</v>
       </c>
       <c r="R104" t="n">
-        <v>6822265</v>
+        <v>6822268</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10747,22 +10747,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129495222</v>
+        <v>129478223</v>
       </c>
       <c r="B105" t="n">
-        <v>79666</v>
+        <v>79695</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10770,21 +10770,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10794,10 +10794,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407454</v>
+        <v>407383</v>
       </c>
       <c r="R105" t="n">
-        <v>6822397</v>
+        <v>6822530</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10844,22 +10844,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129478236</v>
+        <v>129495280</v>
       </c>
       <c r="B106" t="n">
-        <v>79171</v>
+        <v>78833</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10867,21 +10867,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>407330</v>
+        <v>407151</v>
       </c>
       <c r="R106" t="n">
-        <v>6823026</v>
+        <v>6823401</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10941,22 +10941,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129478285</v>
+        <v>129495330</v>
       </c>
       <c r="B107" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10964,21 +10964,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10988,10 +10988,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>407395</v>
+        <v>407076</v>
       </c>
       <c r="R107" t="n">
-        <v>6822535</v>
+        <v>6823195</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11038,19 +11038,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129495348</v>
+        <v>129495354</v>
       </c>
       <c r="B108" t="n">
         <v>79076</v>
@@ -11079,19 +11079,16 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>407363</v>
+        <v>407448</v>
       </c>
       <c r="R108" t="n">
-        <v>6822663</v>
+        <v>6822435</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11132,7 +11129,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11151,7 +11147,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129478299</v>
+        <v>129495363</v>
       </c>
       <c r="B109" t="n">
         <v>79076</v>
@@ -11186,10 +11182,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>407338</v>
+        <v>407371</v>
       </c>
       <c r="R109" t="n">
-        <v>6822715</v>
+        <v>6822492</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,11 +11220,6 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Medel inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -11241,22 +11232,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129478297</v>
+        <v>129495207</v>
       </c>
       <c r="B110" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11264,21 +11255,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11288,10 +11279,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>407319</v>
+        <v>407328</v>
       </c>
       <c r="R110" t="n">
-        <v>6822823</v>
+        <v>6822510</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11326,11 +11317,6 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -11343,22 +11329,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129495365</v>
+        <v>129478210</v>
       </c>
       <c r="B111" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11366,37 +11352,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>407384</v>
+        <v>407518</v>
       </c>
       <c r="R111" t="n">
-        <v>6822512</v>
+        <v>6822380</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11437,29 +11420,28 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129478304</v>
+        <v>129495209</v>
       </c>
       <c r="B112" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11467,21 +11449,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11491,10 +11473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>407389</v>
+        <v>407327</v>
       </c>
       <c r="R112" t="n">
-        <v>6822488</v>
+        <v>6822524</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11541,22 +11523,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129495280</v>
+        <v>129495265</v>
       </c>
       <c r="B113" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11564,34 +11546,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>407151</v>
+        <v>407336</v>
       </c>
       <c r="R113" t="n">
-        <v>6823401</v>
+        <v>6822261</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11632,6 +11617,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -11650,10 +11636,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129495330</v>
+        <v>129495226</v>
       </c>
       <c r="B114" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11661,21 +11647,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11685,10 +11671,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>407076</v>
+        <v>407342</v>
       </c>
       <c r="R114" t="n">
-        <v>6823195</v>
+        <v>6822387</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11747,10 +11733,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129495354</v>
+        <v>129495248</v>
       </c>
       <c r="B115" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11758,21 +11744,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11782,10 +11768,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>407448</v>
+        <v>407059</v>
       </c>
       <c r="R115" t="n">
-        <v>6822435</v>
+        <v>6823213</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11844,10 +11830,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129495363</v>
+        <v>129495216</v>
       </c>
       <c r="B116" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11855,21 +11841,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11879,10 +11865,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>407371</v>
+        <v>407062</v>
       </c>
       <c r="R116" t="n">
-        <v>6822492</v>
+        <v>6823354</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11941,10 +11927,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129495207</v>
+        <v>129495269</v>
       </c>
       <c r="B117" t="n">
-        <v>79695</v>
+        <v>78834</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11952,21 +11938,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11976,10 +11962,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>407328</v>
+        <v>407365</v>
       </c>
       <c r="R117" t="n">
-        <v>6822510</v>
+        <v>6822334</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12038,10 +12024,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129478210</v>
+        <v>129495267</v>
       </c>
       <c r="B118" t="n">
-        <v>79695</v>
+        <v>78834</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12049,21 +12035,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12073,10 +12059,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>407518</v>
+        <v>407351</v>
       </c>
       <c r="R118" t="n">
-        <v>6822380</v>
+        <v>6822325</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12123,22 +12109,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129495209</v>
+        <v>129495217</v>
       </c>
       <c r="B119" t="n">
-        <v>79695</v>
+        <v>79666</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12146,21 +12132,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12170,10 +12156,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>407327</v>
+        <v>407152</v>
       </c>
       <c r="R119" t="n">
-        <v>6822524</v>
+        <v>6823233</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12232,10 +12218,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129495265</v>
+        <v>129478236</v>
       </c>
       <c r="B120" t="n">
-        <v>78834</v>
+        <v>79171</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12243,37 +12229,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>407336</v>
+        <v>407330</v>
       </c>
       <c r="R120" t="n">
-        <v>6822261</v>
+        <v>6823026</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12314,29 +12297,28 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129495226</v>
+        <v>129478285</v>
       </c>
       <c r="B121" t="n">
-        <v>79666</v>
+        <v>78833</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12344,21 +12326,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12368,10 +12350,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>407342</v>
+        <v>407395</v>
       </c>
       <c r="R121" t="n">
-        <v>6822387</v>
+        <v>6822535</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12418,22 +12400,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129495248</v>
+        <v>129495348</v>
       </c>
       <c r="B122" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12441,34 +12423,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>407059</v>
+        <v>407363</v>
       </c>
       <c r="R122" t="n">
-        <v>6823213</v>
+        <v>6822663</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12509,6 +12494,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12527,10 +12513,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129495216</v>
+        <v>129478299</v>
       </c>
       <c r="B123" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12538,21 +12524,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12562,10 +12548,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>407062</v>
+        <v>407338</v>
       </c>
       <c r="R123" t="n">
-        <v>6823354</v>
+        <v>6822715</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12600,6 +12586,11 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Medel inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -12612,22 +12603,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129495269</v>
+        <v>129478297</v>
       </c>
       <c r="B124" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12635,21 +12626,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12659,10 +12650,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>407365</v>
+        <v>407319</v>
       </c>
       <c r="R124" t="n">
-        <v>6822334</v>
+        <v>6822823</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12697,6 +12688,11 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -12709,22 +12705,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129495267</v>
+        <v>129495365</v>
       </c>
       <c r="B125" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12732,34 +12728,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>407351</v>
+        <v>407384</v>
       </c>
       <c r="R125" t="n">
-        <v>6822325</v>
+        <v>6822512</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12800,6 +12799,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -12818,10 +12818,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129495217</v>
+        <v>129478304</v>
       </c>
       <c r="B126" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12829,21 +12829,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12853,10 +12853,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>407152</v>
+        <v>407389</v>
       </c>
       <c r="R126" t="n">
-        <v>6823233</v>
+        <v>6822488</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12903,12 +12903,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -15560,10 +15560,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129495239</v>
+        <v>129495344</v>
       </c>
       <c r="B154" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15571,42 +15571,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>407133</v>
+        <v>407329</v>
       </c>
       <c r="R154" t="n">
-        <v>6823278</v>
+        <v>6822724</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15665,10 +15657,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129495237</v>
+        <v>129495337</v>
       </c>
       <c r="B155" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15676,42 +15668,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>407194</v>
+        <v>407281</v>
       </c>
       <c r="R155" t="n">
-        <v>6823308</v>
+        <v>6822996</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15770,10 +15754,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129495344</v>
+        <v>129495239</v>
       </c>
       <c r="B156" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15781,34 +15765,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>407329</v>
+        <v>407133</v>
       </c>
       <c r="R156" t="n">
-        <v>6822724</v>
+        <v>6823278</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15867,10 +15859,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129495337</v>
+        <v>129495237</v>
       </c>
       <c r="B157" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15878,34 +15870,42 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>407281</v>
+        <v>407194</v>
       </c>
       <c r="R157" t="n">
-        <v>6822996</v>
+        <v>6823308</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -21545,10 +21545,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129495304</v>
+        <v>129495270</v>
       </c>
       <c r="B215" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21556,21 +21556,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21642,10 +21642,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129495364</v>
+        <v>129495220</v>
       </c>
       <c r="B216" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21653,37 +21653,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>407373</v>
+        <v>407451</v>
       </c>
       <c r="R216" t="n">
-        <v>6822509</v>
+        <v>6822425</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -21724,7 +21721,6 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
-      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -21743,10 +21739,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129495353</v>
+        <v>129495304</v>
       </c>
       <c r="B217" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21754,21 +21750,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -21778,10 +21774,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>407394</v>
+        <v>407342</v>
       </c>
       <c r="R217" t="n">
-        <v>6822495</v>
+        <v>6822388</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -21840,10 +21836,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129495306</v>
+        <v>129495364</v>
       </c>
       <c r="B218" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21851,34 +21847,37 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>407349</v>
+        <v>407373</v>
       </c>
       <c r="R218" t="n">
-        <v>6822438</v>
+        <v>6822509</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -21919,6 +21918,7 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -21937,10 +21937,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129478282</v>
+        <v>129495353</v>
       </c>
       <c r="B219" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21948,21 +21948,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -21972,10 +21972,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>407415</v>
+        <v>407394</v>
       </c>
       <c r="R219" t="n">
-        <v>6822315</v>
+        <v>6822495</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22022,22 +22022,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129478224</v>
+        <v>129495306</v>
       </c>
       <c r="B220" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22045,21 +22045,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22069,10 +22069,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>407365</v>
+        <v>407349</v>
       </c>
       <c r="R220" t="n">
-        <v>6822523</v>
+        <v>6822438</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22119,19 +22119,19 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129495277</v>
+        <v>129478282</v>
       </c>
       <c r="B221" t="n">
         <v>78833</v>
@@ -22166,10 +22166,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>407182</v>
+        <v>407415</v>
       </c>
       <c r="R221" t="n">
-        <v>6823012</v>
+        <v>6822315</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22216,19 +22216,19 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129495181</v>
+        <v>129478224</v>
       </c>
       <c r="B222" t="n">
         <v>79695</v>
@@ -22263,10 +22263,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>407197</v>
+        <v>407365</v>
       </c>
       <c r="R222" t="n">
-        <v>6823283</v>
+        <v>6822523</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22313,22 +22313,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129495171</v>
+        <v>129495277</v>
       </c>
       <c r="B223" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22336,21 +22336,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22360,10 +22360,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>407073</v>
+        <v>407182</v>
       </c>
       <c r="R223" t="n">
-        <v>6823197</v>
+        <v>6823012</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22422,10 +22422,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129495270</v>
+        <v>129495181</v>
       </c>
       <c r="B224" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22433,21 +22433,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -22457,10 +22457,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>407342</v>
+        <v>407197</v>
       </c>
       <c r="R224" t="n">
-        <v>6822388</v>
+        <v>6823283</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22519,10 +22519,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129495220</v>
+        <v>129495171</v>
       </c>
       <c r="B225" t="n">
-        <v>79666</v>
+        <v>79695</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22530,21 +22530,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22554,10 +22554,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>407451</v>
+        <v>407073</v>
       </c>
       <c r="R225" t="n">
-        <v>6822425</v>
+        <v>6823197</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>

--- a/artfynd/A 44936-2025 artfynd.xlsx
+++ b/artfynd/A 44936-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129495273</v>
+        <v>129495314</v>
       </c>
       <c r="B3" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407323</v>
+        <v>407305</v>
       </c>
       <c r="R3" t="n">
-        <v>6822521</v>
+        <v>6822639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129495264</v>
+        <v>129495309</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407464</v>
+        <v>407320</v>
       </c>
       <c r="R4" t="n">
-        <v>6822329</v>
+        <v>6822525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129495218</v>
+        <v>129478200</v>
       </c>
       <c r="B5" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407405</v>
+        <v>407203</v>
       </c>
       <c r="R5" t="n">
-        <v>6822602</v>
+        <v>6823039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,22 +1059,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129495256</v>
+        <v>129478308</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,37 +1082,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407292</v>
+        <v>407271</v>
       </c>
       <c r="R6" t="n">
-        <v>6823105</v>
+        <v>6822740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,29 +1150,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129495314</v>
+        <v>129478209</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1207,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407305</v>
+        <v>407521</v>
       </c>
       <c r="R7" t="n">
-        <v>6822639</v>
+        <v>6822449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,22 +1253,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129495309</v>
+        <v>129495182</v>
       </c>
       <c r="B8" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,21 +1276,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407320</v>
+        <v>407173</v>
       </c>
       <c r="R8" t="n">
-        <v>6822525</v>
+        <v>6823280</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129478200</v>
+        <v>129495273</v>
       </c>
       <c r="B9" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407203</v>
+        <v>407323</v>
       </c>
       <c r="R9" t="n">
-        <v>6823039</v>
+        <v>6822521</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,22 +1447,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129478308</v>
+        <v>129495264</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1474,21 +1470,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1498,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407271</v>
+        <v>407464</v>
       </c>
       <c r="R10" t="n">
-        <v>6822740</v>
+        <v>6822329</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,22 +1544,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129478209</v>
+        <v>129495218</v>
       </c>
       <c r="B11" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1571,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1595,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407521</v>
+        <v>407405</v>
       </c>
       <c r="R11" t="n">
-        <v>6822449</v>
+        <v>6822602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,22 +1641,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129495182</v>
+        <v>129495256</v>
       </c>
       <c r="B12" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,34 +1664,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407173</v>
+        <v>407292</v>
       </c>
       <c r="R12" t="n">
-        <v>6823280</v>
+        <v>6823105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1735,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2635,48 +2635,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129495320</v>
+        <v>129495272</v>
       </c>
       <c r="B22" t="n">
-        <v>91772</v>
+        <v>78839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407346</v>
+        <v>407368</v>
       </c>
       <c r="R22" t="n">
-        <v>6822297</v>
+        <v>6822493</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,7 +2714,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2736,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129495305</v>
+        <v>129478253</v>
       </c>
       <c r="B23" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2747,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407354</v>
+        <v>407276</v>
       </c>
       <c r="R23" t="n">
-        <v>6822434</v>
+        <v>6822880</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2821,22 +2817,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129495307</v>
+        <v>129495259</v>
       </c>
       <c r="B24" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,37 +2840,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407360</v>
+        <v>407405</v>
       </c>
       <c r="R24" t="n">
-        <v>6822502</v>
+        <v>6822617</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,7 +2908,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2934,45 +2926,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129478272</v>
+        <v>129495320</v>
       </c>
       <c r="B25" t="n">
-        <v>78838</v>
+        <v>91772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407279</v>
+        <v>407346</v>
       </c>
       <c r="R25" t="n">
-        <v>6823111</v>
+        <v>6822297</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,28 +3008,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129478306</v>
+        <v>129495305</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3042,21 +3038,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3066,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407334</v>
+        <v>407354</v>
       </c>
       <c r="R26" t="n">
-        <v>6822621</v>
+        <v>6822434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,11 +3100,6 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Medel inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3121,19 +3112,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129495289</v>
+        <v>129495307</v>
       </c>
       <c r="B27" t="n">
         <v>78838</v>
@@ -3162,16 +3153,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407408</v>
+        <v>407360</v>
       </c>
       <c r="R27" t="n">
-        <v>6822618</v>
+        <v>6822502</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,17 +3200,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>14.05</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3235,10 +3225,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129495326</v>
+        <v>129478272</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3246,21 +3236,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3270,10 +3260,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407127</v>
+        <v>407279</v>
       </c>
       <c r="R28" t="n">
-        <v>6823075</v>
+        <v>6823111</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3320,19 +3310,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129495343</v>
+        <v>129478306</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3361,19 +3351,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407333</v>
+        <v>407334</v>
       </c>
       <c r="R29" t="n">
-        <v>6822764</v>
+        <v>6822621</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3410,7 +3397,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40 meter.</t>
+          <t>Medel inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3419,29 +3406,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129495205</v>
+        <v>129495289</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3449,21 +3435,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3473,10 +3459,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407374</v>
+        <v>407408</v>
       </c>
       <c r="R30" t="n">
-        <v>6822521</v>
+        <v>6822618</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,6 +3495,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>14.05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3535,10 +3526,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129478286</v>
+        <v>129495326</v>
       </c>
       <c r="B31" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3546,21 +3537,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3570,10 +3561,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407384</v>
+        <v>407127</v>
       </c>
       <c r="R31" t="n">
-        <v>6822529</v>
+        <v>6823075</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3620,22 +3611,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129495316</v>
+        <v>129495343</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3643,34 +3634,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407264</v>
+        <v>407333</v>
       </c>
       <c r="R32" t="n">
-        <v>6822669</v>
+        <v>6822764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3705,12 +3699,18 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40 meter.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3729,10 +3729,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129495322</v>
+        <v>129495205</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3740,21 +3740,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407206</v>
+        <v>407374</v>
       </c>
       <c r="R33" t="n">
-        <v>6822872</v>
+        <v>6822521</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3826,10 +3826,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129478232</v>
+        <v>129478286</v>
       </c>
       <c r="B34" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3837,21 +3837,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407252</v>
+        <v>407384</v>
       </c>
       <c r="R34" t="n">
-        <v>6822721</v>
+        <v>6822529</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129495302</v>
+        <v>129495316</v>
       </c>
       <c r="B35" t="n">
         <v>78838</v>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407379</v>
+        <v>407264</v>
       </c>
       <c r="R35" t="n">
-        <v>6822366</v>
+        <v>6822669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129495342</v>
+        <v>129495322</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407301</v>
+        <v>407206</v>
       </c>
       <c r="R36" t="n">
-        <v>6822802</v>
+        <v>6822872</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4117,7 +4117,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129495168</v>
+        <v>129478232</v>
       </c>
       <c r="B37" t="n">
         <v>79700</v>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407208</v>
+        <v>407252</v>
       </c>
       <c r="R37" t="n">
-        <v>6822972</v>
+        <v>6822721</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4202,22 +4202,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129495272</v>
+        <v>129495302</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4225,21 +4225,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>407368</v>
+        <v>407379</v>
       </c>
       <c r="R38" t="n">
-        <v>6822493</v>
+        <v>6822366</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4311,10 +4311,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129478253</v>
+        <v>129495342</v>
       </c>
       <c r="B39" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4322,21 +4322,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>407276</v>
+        <v>407301</v>
       </c>
       <c r="R39" t="n">
-        <v>6822880</v>
+        <v>6822802</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4396,22 +4396,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129495259</v>
+        <v>129495168</v>
       </c>
       <c r="B40" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4419,21 +4419,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>407405</v>
+        <v>407208</v>
       </c>
       <c r="R40" t="n">
-        <v>6822617</v>
+        <v>6822972</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129478260</v>
+        <v>129495291</v>
       </c>
       <c r="B51" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5499,21 +5499,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407390</v>
+        <v>407457</v>
       </c>
       <c r="R51" t="n">
-        <v>6822446</v>
+        <v>6822425</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5573,22 +5573,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129495228</v>
+        <v>129478300</v>
       </c>
       <c r="B52" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5596,21 +5596,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>407368</v>
+        <v>407468</v>
       </c>
       <c r="R52" t="n">
-        <v>6822481</v>
+        <v>6822633</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5670,22 +5670,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129478262</v>
+        <v>129495285</v>
       </c>
       <c r="B53" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5693,21 +5693,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5717,10 +5717,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407384</v>
+        <v>407222</v>
       </c>
       <c r="R53" t="n">
-        <v>6822532</v>
+        <v>6823145</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5767,22 +5767,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129495291</v>
+        <v>129495194</v>
       </c>
       <c r="B54" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5790,21 +5790,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407457</v>
+        <v>407452</v>
       </c>
       <c r="R54" t="n">
-        <v>6822425</v>
+        <v>6822376</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5876,10 +5876,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129478300</v>
+        <v>129495286</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5887,21 +5887,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407468</v>
+        <v>407274</v>
       </c>
       <c r="R55" t="n">
-        <v>6822633</v>
+        <v>6823142</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5961,22 +5961,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129495285</v>
+        <v>129478302</v>
       </c>
       <c r="B56" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5984,21 +5984,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407222</v>
+        <v>407408</v>
       </c>
       <c r="R56" t="n">
-        <v>6823145</v>
+        <v>6822212</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6058,22 +6058,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129495194</v>
+        <v>129478281</v>
       </c>
       <c r="B57" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407452</v>
+        <v>407417</v>
       </c>
       <c r="R57" t="n">
-        <v>6822376</v>
+        <v>6822269</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6155,22 +6155,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129495286</v>
+        <v>129478298</v>
       </c>
       <c r="B58" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6178,21 +6178,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6202,10 +6202,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407274</v>
+        <v>407339</v>
       </c>
       <c r="R58" t="n">
-        <v>6823142</v>
+        <v>6822779</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6240,6 +6240,11 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6252,22 +6257,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129478302</v>
+        <v>129495308</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6275,21 +6280,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6299,10 +6304,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407408</v>
+        <v>407326</v>
       </c>
       <c r="R59" t="n">
-        <v>6822212</v>
+        <v>6822521</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6349,22 +6354,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129478281</v>
+        <v>129478305</v>
       </c>
       <c r="B60" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6372,21 +6377,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6396,10 +6401,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407417</v>
+        <v>407395</v>
       </c>
       <c r="R60" t="n">
-        <v>6822269</v>
+        <v>6822461</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6458,10 +6463,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129478298</v>
+        <v>129495233</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6469,34 +6474,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407339</v>
+        <v>407317</v>
       </c>
       <c r="R61" t="n">
-        <v>6822779</v>
+        <v>6822622</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6531,11 +6544,6 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6548,22 +6556,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129495308</v>
+        <v>129478260</v>
       </c>
       <c r="B62" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6571,21 +6579,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6595,10 +6603,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407326</v>
+        <v>407390</v>
       </c>
       <c r="R62" t="n">
-        <v>6822521</v>
+        <v>6822446</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6645,22 +6653,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129478305</v>
+        <v>129495228</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6668,21 +6676,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6692,10 +6700,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407395</v>
+        <v>407368</v>
       </c>
       <c r="R63" t="n">
-        <v>6822461</v>
+        <v>6822481</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6742,22 +6750,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129495233</v>
+        <v>129478262</v>
       </c>
       <c r="B64" t="n">
-        <v>57896</v>
+        <v>78839</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6765,42 +6773,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407317</v>
+        <v>407384</v>
       </c>
       <c r="R64" t="n">
-        <v>6822622</v>
+        <v>6822532</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6847,12 +6847,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -9203,10 +9203,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129478252</v>
+        <v>129495169</v>
       </c>
       <c r="B89" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9214,21 +9214,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9238,10 +9238,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>407320</v>
+        <v>407109</v>
       </c>
       <c r="R89" t="n">
-        <v>6823016</v>
+        <v>6823069</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9288,22 +9288,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129495266</v>
+        <v>129495341</v>
       </c>
       <c r="B90" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9311,21 +9311,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>407345</v>
+        <v>407305</v>
       </c>
       <c r="R90" t="n">
-        <v>6822265</v>
+        <v>6822819</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9397,10 +9397,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129495222</v>
+        <v>129495371</v>
       </c>
       <c r="B91" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9408,21 +9408,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9432,10 +9432,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>407454</v>
+        <v>407244</v>
       </c>
       <c r="R91" t="n">
-        <v>6822397</v>
+        <v>6822729</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9494,10 +9494,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129495169</v>
+        <v>129478276</v>
       </c>
       <c r="B92" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9505,21 +9505,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9529,10 +9529,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>407109</v>
+        <v>407535</v>
       </c>
       <c r="R92" t="n">
-        <v>6823069</v>
+        <v>6822520</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9579,19 +9579,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129495341</v>
+        <v>129495359</v>
       </c>
       <c r="B93" t="n">
         <v>79081</v>
@@ -9620,16 +9620,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>407305</v>
+        <v>407400</v>
       </c>
       <c r="R93" t="n">
-        <v>6822819</v>
+        <v>6822209</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9670,6 +9673,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9688,10 +9692,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129495371</v>
+        <v>129495183</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9699,21 +9703,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9723,10 +9727,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>407244</v>
+        <v>407209</v>
       </c>
       <c r="R94" t="n">
-        <v>6822729</v>
+        <v>6823207</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9785,10 +9789,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129478276</v>
+        <v>129495187</v>
       </c>
       <c r="B95" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9796,21 +9800,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9820,10 +9824,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>407535</v>
+        <v>407280</v>
       </c>
       <c r="R95" t="n">
-        <v>6822520</v>
+        <v>6822879</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9870,19 +9874,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129495359</v>
+        <v>129495336</v>
       </c>
       <c r="B96" t="n">
         <v>79081</v>
@@ -9911,19 +9915,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>407400</v>
+        <v>407088</v>
       </c>
       <c r="R96" t="n">
-        <v>6822209</v>
+        <v>6823461</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9964,7 +9965,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -9983,7 +9983,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129495183</v>
+        <v>129495199</v>
       </c>
       <c r="B97" t="n">
         <v>79700</v>
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>407209</v>
+        <v>407337</v>
       </c>
       <c r="R97" t="n">
-        <v>6823207</v>
+        <v>6822261</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10080,7 +10080,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129495187</v>
+        <v>129478213</v>
       </c>
       <c r="B98" t="n">
         <v>79700</v>
@@ -10115,10 +10115,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>407280</v>
+        <v>407414</v>
       </c>
       <c r="R98" t="n">
-        <v>6822879</v>
+        <v>6822268</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10165,22 +10165,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129495336</v>
+        <v>129478223</v>
       </c>
       <c r="B99" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10188,21 +10188,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>407088</v>
+        <v>407383</v>
       </c>
       <c r="R99" t="n">
-        <v>6823461</v>
+        <v>6822530</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10262,19 +10262,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129495199</v>
+        <v>129495210</v>
       </c>
       <c r="B100" t="n">
         <v>79700</v>
@@ -10309,10 +10309,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>407337</v>
+        <v>407328</v>
       </c>
       <c r="R100" t="n">
-        <v>6822261</v>
+        <v>6822512</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10371,7 +10371,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129478213</v>
+        <v>129478202</v>
       </c>
       <c r="B101" t="n">
         <v>79700</v>
@@ -10406,10 +10406,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>407414</v>
+        <v>407245</v>
       </c>
       <c r="R101" t="n">
-        <v>6822268</v>
+        <v>6823196</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10468,7 +10468,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129478223</v>
+        <v>129495177</v>
       </c>
       <c r="B102" t="n">
         <v>79700</v>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>407383</v>
+        <v>407097</v>
       </c>
       <c r="R102" t="n">
-        <v>6822530</v>
+        <v>6823458</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10553,22 +10553,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129495210</v>
+        <v>129478252</v>
       </c>
       <c r="B103" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10576,21 +10576,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10600,10 +10600,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>407328</v>
+        <v>407320</v>
       </c>
       <c r="R103" t="n">
-        <v>6822512</v>
+        <v>6823016</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10650,22 +10650,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129478202</v>
+        <v>129495266</v>
       </c>
       <c r="B104" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10673,21 +10673,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10697,10 +10697,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>407245</v>
+        <v>407345</v>
       </c>
       <c r="R104" t="n">
-        <v>6823196</v>
+        <v>6822265</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10747,22 +10747,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129495177</v>
+        <v>129495222</v>
       </c>
       <c r="B105" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10770,21 +10770,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10794,10 +10794,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>407097</v>
+        <v>407454</v>
       </c>
       <c r="R105" t="n">
-        <v>6823458</v>
+        <v>6822397</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14687,10 +14687,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129495170</v>
+        <v>129478254</v>
       </c>
       <c r="B145" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14698,21 +14698,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14722,10 +14722,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>407098</v>
+        <v>407409</v>
       </c>
       <c r="R145" t="n">
-        <v>6823137</v>
+        <v>6822618</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14772,22 +14772,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129495191</v>
+        <v>129478258</v>
       </c>
       <c r="B146" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14795,21 +14795,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14819,10 +14819,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>407450</v>
+        <v>407417</v>
       </c>
       <c r="R146" t="n">
-        <v>6822424</v>
+        <v>6822268</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14869,22 +14869,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129478265</v>
+        <v>129478247</v>
       </c>
       <c r="B147" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14892,21 +14892,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14916,10 +14916,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>407205</v>
+        <v>407141</v>
       </c>
       <c r="R147" t="n">
-        <v>6823043</v>
+        <v>6823420</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -14978,10 +14978,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129478279</v>
+        <v>129495191</v>
       </c>
       <c r="B148" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14989,21 +14989,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>407519</v>
+        <v>407450</v>
       </c>
       <c r="R148" t="n">
-        <v>6822447</v>
+        <v>6822424</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15063,19 +15063,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129495288</v>
+        <v>129478265</v>
       </c>
       <c r="B149" t="n">
         <v>78838</v>
@@ -15110,10 +15110,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>407287</v>
+        <v>407205</v>
       </c>
       <c r="R149" t="n">
-        <v>6822985</v>
+        <v>6823043</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15160,22 +15160,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129495176</v>
+        <v>129478279</v>
       </c>
       <c r="B150" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15183,21 +15183,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15207,10 +15207,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>407099</v>
+        <v>407519</v>
       </c>
       <c r="R150" t="n">
-        <v>6823473</v>
+        <v>6822447</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15257,22 +15257,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129478254</v>
+        <v>129495288</v>
       </c>
       <c r="B151" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15280,21 +15280,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>407409</v>
+        <v>407287</v>
       </c>
       <c r="R151" t="n">
-        <v>6822618</v>
+        <v>6822985</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15354,22 +15354,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129478258</v>
+        <v>129495176</v>
       </c>
       <c r="B152" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15377,21 +15377,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15401,10 +15401,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>407417</v>
+        <v>407099</v>
       </c>
       <c r="R152" t="n">
-        <v>6822268</v>
+        <v>6823473</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15451,22 +15451,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129478247</v>
+        <v>129495170</v>
       </c>
       <c r="B153" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15474,21 +15474,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15498,10 +15498,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>407141</v>
+        <v>407098</v>
       </c>
       <c r="R153" t="n">
-        <v>6823420</v>
+        <v>6823137</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15548,22 +15548,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129495239</v>
+        <v>129495344</v>
       </c>
       <c r="B154" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15571,42 +15571,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>407133</v>
+        <v>407329</v>
       </c>
       <c r="R154" t="n">
-        <v>6823278</v>
+        <v>6822724</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15665,10 +15657,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129495237</v>
+        <v>129478231</v>
       </c>
       <c r="B155" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15676,42 +15668,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>407194</v>
+        <v>407270</v>
       </c>
       <c r="R155" t="n">
-        <v>6823308</v>
+        <v>6822722</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15758,22 +15742,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129478251</v>
+        <v>129478271</v>
       </c>
       <c r="B156" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15781,21 +15765,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15805,10 +15789,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>407266</v>
+        <v>407272</v>
       </c>
       <c r="R156" t="n">
-        <v>6823123</v>
+        <v>6823147</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15867,10 +15851,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129495225</v>
+        <v>129495337</v>
       </c>
       <c r="B157" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15878,21 +15862,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -15902,10 +15886,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>407359</v>
+        <v>407281</v>
       </c>
       <c r="R157" t="n">
-        <v>6822322</v>
+        <v>6822996</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -15964,10 +15948,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129495229</v>
+        <v>129478228</v>
       </c>
       <c r="B158" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15975,21 +15959,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -15999,10 +15983,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>407299</v>
+        <v>407325</v>
       </c>
       <c r="R158" t="n">
-        <v>6822612</v>
+        <v>6822646</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16049,22 +16033,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129495344</v>
+        <v>129478217</v>
       </c>
       <c r="B159" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16072,21 +16056,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16096,10 +16080,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>407329</v>
+        <v>407385</v>
       </c>
       <c r="R159" t="n">
-        <v>6822724</v>
+        <v>6822314</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16146,22 +16130,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129478231</v>
+        <v>129495312</v>
       </c>
       <c r="B160" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16169,21 +16153,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16193,10 +16177,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>407270</v>
+        <v>407301</v>
       </c>
       <c r="R160" t="n">
-        <v>6822722</v>
+        <v>6822575</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16243,22 +16227,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129478271</v>
+        <v>129495202</v>
       </c>
       <c r="B161" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16266,21 +16250,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16290,10 +16274,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>407272</v>
+        <v>407355</v>
       </c>
       <c r="R161" t="n">
-        <v>6823147</v>
+        <v>6822321</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16340,22 +16324,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129495337</v>
+        <v>129478227</v>
       </c>
       <c r="B162" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16363,21 +16347,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16387,10 +16371,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>407281</v>
+        <v>407333</v>
       </c>
       <c r="R162" t="n">
-        <v>6822996</v>
+        <v>6822601</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16437,19 +16421,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129478228</v>
+        <v>129478220</v>
       </c>
       <c r="B163" t="n">
         <v>79700</v>
@@ -16484,10 +16468,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>407325</v>
+        <v>407390</v>
       </c>
       <c r="R163" t="n">
-        <v>6822646</v>
+        <v>6822450</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16546,7 +16530,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129478217</v>
+        <v>129495174</v>
       </c>
       <c r="B164" t="n">
         <v>79700</v>
@@ -16581,10 +16565,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>407385</v>
+        <v>407052</v>
       </c>
       <c r="R164" t="n">
-        <v>6822314</v>
+        <v>6823345</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16631,22 +16615,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129495312</v>
+        <v>129478204</v>
       </c>
       <c r="B165" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16654,21 +16638,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -16678,10 +16662,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>407301</v>
+        <v>407300</v>
       </c>
       <c r="R165" t="n">
-        <v>6822575</v>
+        <v>6823030</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -16728,22 +16712,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129495202</v>
+        <v>129495239</v>
       </c>
       <c r="B166" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16751,34 +16735,42 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>407355</v>
+        <v>407133</v>
       </c>
       <c r="R166" t="n">
-        <v>6822321</v>
+        <v>6823278</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -16837,10 +16829,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129478227</v>
+        <v>129495237</v>
       </c>
       <c r="B167" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16848,34 +16840,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>407333</v>
+        <v>407194</v>
       </c>
       <c r="R167" t="n">
-        <v>6822601</v>
+        <v>6823308</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -16922,22 +16922,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129478220</v>
+        <v>129478251</v>
       </c>
       <c r="B168" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16945,21 +16945,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16969,10 +16969,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>407390</v>
+        <v>407266</v>
       </c>
       <c r="R168" t="n">
-        <v>6822450</v>
+        <v>6823123</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17031,10 +17031,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129495174</v>
+        <v>129495225</v>
       </c>
       <c r="B169" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17042,21 +17042,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17066,10 +17066,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>407052</v>
+        <v>407359</v>
       </c>
       <c r="R169" t="n">
-        <v>6823345</v>
+        <v>6822322</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17128,10 +17128,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129478204</v>
+        <v>129495229</v>
       </c>
       <c r="B170" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17139,21 +17139,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17163,10 +17163,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>407300</v>
+        <v>407299</v>
       </c>
       <c r="R170" t="n">
-        <v>6823030</v>
+        <v>6822612</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17213,12 +17213,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -18702,10 +18702,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129495325</v>
+        <v>129478246</v>
       </c>
       <c r="B186" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18713,21 +18713,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18737,10 +18737,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>407135</v>
+        <v>407112</v>
       </c>
       <c r="R186" t="n">
-        <v>6823090</v>
+        <v>6823299</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18787,22 +18787,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129478214</v>
+        <v>129495262</v>
       </c>
       <c r="B187" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18810,21 +18810,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18834,10 +18834,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>407405</v>
+        <v>407456</v>
       </c>
       <c r="R187" t="n">
-        <v>6822277</v>
+        <v>6822397</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18884,22 +18884,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129478278</v>
+        <v>129495325</v>
       </c>
       <c r="B188" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18907,21 +18907,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18931,10 +18931,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>407504</v>
+        <v>407135</v>
       </c>
       <c r="R188" t="n">
-        <v>6822459</v>
+        <v>6823090</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -18981,22 +18981,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129478303</v>
+        <v>129478214</v>
       </c>
       <c r="B189" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19004,21 +19004,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19028,10 +19028,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>407418</v>
+        <v>407405</v>
       </c>
       <c r="R189" t="n">
-        <v>6822356</v>
+        <v>6822277</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19090,7 +19090,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129478266</v>
+        <v>129478278</v>
       </c>
       <c r="B190" t="n">
         <v>78838</v>
@@ -19125,10 +19125,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>407115</v>
+        <v>407504</v>
       </c>
       <c r="R190" t="n">
-        <v>6823174</v>
+        <v>6822459</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19187,10 +19187,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129495206</v>
+        <v>129478303</v>
       </c>
       <c r="B191" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19198,21 +19198,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19222,10 +19222,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>407378</v>
+        <v>407418</v>
       </c>
       <c r="R191" t="n">
-        <v>6822506</v>
+        <v>6822356</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19272,65 +19272,57 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129495232</v>
+        <v>129478266</v>
       </c>
       <c r="B192" t="n">
-        <v>56926</v>
+        <v>78838</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>407256</v>
+        <v>407115</v>
       </c>
       <c r="R192" t="n">
-        <v>6823010</v>
+        <v>6823174</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19377,22 +19369,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129478246</v>
+        <v>129495206</v>
       </c>
       <c r="B193" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19400,21 +19392,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19424,10 +19416,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>407112</v>
+        <v>407378</v>
       </c>
       <c r="R193" t="n">
-        <v>6823299</v>
+        <v>6822506</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19474,22 +19466,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129495262</v>
+        <v>129478238</v>
       </c>
       <c r="B194" t="n">
-        <v>78839</v>
+        <v>91620</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19497,21 +19489,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19521,10 +19513,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>407456</v>
+        <v>407386</v>
       </c>
       <c r="R194" t="n">
-        <v>6822397</v>
+        <v>6822322</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19559,6 +19551,11 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
@@ -19571,57 +19568,65 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129478238</v>
+        <v>129495232</v>
       </c>
       <c r="B195" t="n">
-        <v>91620</v>
+        <v>56926</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>407386</v>
+        <v>407256</v>
       </c>
       <c r="R195" t="n">
-        <v>6822322</v>
+        <v>6823010</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19656,11 +19661,6 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
@@ -19673,12 +19673,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
@@ -21056,10 +21056,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129495270</v>
+        <v>129478224</v>
       </c>
       <c r="B210" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21067,21 +21067,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21091,10 +21091,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>407342</v>
+        <v>407365</v>
       </c>
       <c r="R210" t="n">
-        <v>6822388</v>
+        <v>6822523</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21141,22 +21141,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129495220</v>
+        <v>129495277</v>
       </c>
       <c r="B211" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21164,21 +21164,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21188,10 +21188,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>407451</v>
+        <v>407182</v>
       </c>
       <c r="R211" t="n">
-        <v>6822425</v>
+        <v>6823012</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21250,7 +21250,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129478224</v>
+        <v>129495181</v>
       </c>
       <c r="B212" t="n">
         <v>79700</v>
@@ -21285,10 +21285,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>407365</v>
+        <v>407197</v>
       </c>
       <c r="R212" t="n">
-        <v>6822523</v>
+        <v>6823283</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21335,19 +21335,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129495277</v>
+        <v>129495304</v>
       </c>
       <c r="B213" t="n">
         <v>78838</v>
@@ -21382,10 +21382,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>407182</v>
+        <v>407342</v>
       </c>
       <c r="R213" t="n">
-        <v>6823012</v>
+        <v>6822388</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21444,7 +21444,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129495181</v>
+        <v>129495171</v>
       </c>
       <c r="B214" t="n">
         <v>79700</v>
@@ -21479,10 +21479,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>407197</v>
+        <v>407073</v>
       </c>
       <c r="R214" t="n">
-        <v>6823283</v>
+        <v>6823197</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21541,10 +21541,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129495304</v>
+        <v>129495364</v>
       </c>
       <c r="B215" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21552,34 +21552,37 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>407342</v>
+        <v>407373</v>
       </c>
       <c r="R215" t="n">
-        <v>6822388</v>
+        <v>6822509</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21620,6 +21623,7 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -21638,10 +21642,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129495171</v>
+        <v>129495296</v>
       </c>
       <c r="B216" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21649,21 +21653,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -21673,10 +21677,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>407073</v>
+        <v>407469</v>
       </c>
       <c r="R216" t="n">
-        <v>6823197</v>
+        <v>6822344</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -21735,10 +21739,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129495364</v>
+        <v>129478206</v>
       </c>
       <c r="B217" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21746,37 +21750,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>407373</v>
+        <v>407513</v>
       </c>
       <c r="R217" t="n">
-        <v>6822509</v>
+        <v>6822490</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -21817,29 +21818,28 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
-      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129495296</v>
+        <v>129495353</v>
       </c>
       <c r="B218" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21847,21 +21847,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -21871,10 +21871,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>407469</v>
+        <v>407394</v>
       </c>
       <c r="R218" t="n">
-        <v>6822344</v>
+        <v>6822495</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129478206</v>
+        <v>129495310</v>
       </c>
       <c r="B219" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21944,34 +21944,37 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>407513</v>
+        <v>407318</v>
       </c>
       <c r="R219" t="n">
-        <v>6822490</v>
+        <v>6822539</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22012,28 +22015,29 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129495353</v>
+        <v>129495211</v>
       </c>
       <c r="B220" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22041,21 +22045,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22065,10 +22069,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>407394</v>
+        <v>407312</v>
       </c>
       <c r="R220" t="n">
-        <v>6822495</v>
+        <v>6822520</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22127,7 +22131,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129495310</v>
+        <v>129495306</v>
       </c>
       <c r="B221" t="n">
         <v>78838</v>
@@ -22156,19 +22160,16 @@
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>407318</v>
+        <v>407349</v>
       </c>
       <c r="R221" t="n">
-        <v>6822539</v>
+        <v>6822438</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22209,7 +22210,6 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -22228,10 +22228,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129495211</v>
+        <v>129478277</v>
       </c>
       <c r="B222" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22239,21 +22239,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22263,10 +22263,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>407312</v>
+        <v>407513</v>
       </c>
       <c r="R222" t="n">
-        <v>6822520</v>
+        <v>6822486</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22313,19 +22313,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129495306</v>
+        <v>129478282</v>
       </c>
       <c r="B223" t="n">
         <v>78838</v>
@@ -22360,10 +22360,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>407349</v>
+        <v>407415</v>
       </c>
       <c r="R223" t="n">
-        <v>6822438</v>
+        <v>6822315</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22410,22 +22410,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129478277</v>
+        <v>129495270</v>
       </c>
       <c r="B224" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22433,21 +22433,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -22457,10 +22457,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>407513</v>
+        <v>407342</v>
       </c>
       <c r="R224" t="n">
-        <v>6822486</v>
+        <v>6822388</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22507,22 +22507,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129478282</v>
+        <v>129495220</v>
       </c>
       <c r="B225" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22530,21 +22530,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22554,10 +22554,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>407415</v>
+        <v>407451</v>
       </c>
       <c r="R225" t="n">
-        <v>6822315</v>
+        <v>6822425</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22604,22 +22604,22 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129478235</v>
+        <v>129478284</v>
       </c>
       <c r="B226" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22627,21 +22627,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22651,10 +22651,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>407342</v>
+        <v>407395</v>
       </c>
       <c r="R226" t="n">
-        <v>6822967</v>
+        <v>6822450</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -22695,7 +22695,6 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
-      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
@@ -22714,10 +22713,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129478248</v>
+        <v>129495185</v>
       </c>
       <c r="B227" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22725,21 +22724,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -22749,10 +22748,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>407184</v>
+        <v>407289</v>
       </c>
       <c r="R227" t="n">
-        <v>6823444</v>
+        <v>6822962</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -22799,19 +22798,19 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129478284</v>
+        <v>129495300</v>
       </c>
       <c r="B228" t="n">
         <v>78838</v>
@@ -22846,10 +22845,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>407395</v>
+        <v>407339</v>
       </c>
       <c r="R228" t="n">
-        <v>6822450</v>
+        <v>6822262</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -22896,22 +22895,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129495185</v>
+        <v>129495338</v>
       </c>
       <c r="B229" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22919,34 +22918,37 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>407289</v>
+        <v>407288</v>
       </c>
       <c r="R229" t="n">
-        <v>6822962</v>
+        <v>6822980</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -22981,12 +22983,18 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 40 m.</t>
+        </is>
+      </c>
       <c r="AD229" t="b">
         <v>0</v>
       </c>
       <c r="AE229" t="b">
         <v>0</v>
       </c>
+      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
@@ -23005,10 +23013,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129495300</v>
+        <v>129495368</v>
       </c>
       <c r="B230" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23016,21 +23024,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23040,10 +23048,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>407339</v>
+        <v>407258</v>
       </c>
       <c r="R230" t="n">
-        <v>6822262</v>
+        <v>6822667</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23102,7 +23110,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129495338</v>
+        <v>129495358</v>
       </c>
       <c r="B231" t="n">
         <v>79081</v>
@@ -23131,19 +23139,16 @@
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>407288</v>
+        <v>407387</v>
       </c>
       <c r="R231" t="n">
-        <v>6822980</v>
+        <v>6822160</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23178,18 +23183,12 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 40 m.</t>
-        </is>
-      </c>
       <c r="AD231" t="b">
         <v>0</v>
       </c>
       <c r="AE231" t="b">
         <v>0</v>
       </c>
-      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
@@ -23208,10 +23207,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129495368</v>
+        <v>129478229</v>
       </c>
       <c r="B232" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23219,21 +23218,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23243,10 +23242,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>407258</v>
+        <v>407311</v>
       </c>
       <c r="R232" t="n">
-        <v>6822667</v>
+        <v>6822643</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23293,22 +23292,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129495358</v>
+        <v>129478267</v>
       </c>
       <c r="B233" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23316,21 +23315,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23340,10 +23339,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>407387</v>
+        <v>407112</v>
       </c>
       <c r="R233" t="n">
-        <v>6822160</v>
+        <v>6823299</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23390,22 +23389,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129478229</v>
+        <v>129495297</v>
       </c>
       <c r="B234" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23413,21 +23412,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23437,10 +23436,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>407311</v>
+        <v>407473</v>
       </c>
       <c r="R234" t="n">
-        <v>6822643</v>
+        <v>6822338</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -23487,22 +23486,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129478267</v>
+        <v>129495172</v>
       </c>
       <c r="B235" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23510,21 +23509,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -23534,10 +23533,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>407112</v>
+        <v>407071</v>
       </c>
       <c r="R235" t="n">
-        <v>6823299</v>
+        <v>6823251</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23584,22 +23583,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129495297</v>
+        <v>129495355</v>
       </c>
       <c r="B236" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23607,21 +23606,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -23631,10 +23630,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>407473</v>
+        <v>407467</v>
       </c>
       <c r="R236" t="n">
-        <v>6822338</v>
+        <v>6822368</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -23693,10 +23692,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129495172</v>
+        <v>129495242</v>
       </c>
       <c r="B237" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23704,34 +23703,42 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>407071</v>
+        <v>407257</v>
       </c>
       <c r="R237" t="n">
-        <v>6823251</v>
+        <v>6823042</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -23790,10 +23797,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129495355</v>
+        <v>129478235</v>
       </c>
       <c r="B238" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23801,21 +23808,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -23825,10 +23832,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>407467</v>
+        <v>407342</v>
       </c>
       <c r="R238" t="n">
-        <v>6822368</v>
+        <v>6822967</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -23869,28 +23876,29 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
+      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129495242</v>
+        <v>129478248</v>
       </c>
       <c r="B239" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23898,42 +23906,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>407257</v>
+        <v>407184</v>
       </c>
       <c r="R239" t="n">
-        <v>6823042</v>
+        <v>6823444</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -23980,12 +23980,12 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
@@ -25847,10 +25847,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129478245</v>
+        <v>129495301</v>
       </c>
       <c r="B259" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -25858,21 +25858,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -25882,10 +25882,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>407208</v>
+        <v>407337</v>
       </c>
       <c r="R259" t="n">
-        <v>6823030</v>
+        <v>6822261</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -25932,22 +25932,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129495253</v>
+        <v>129495351</v>
       </c>
       <c r="B260" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -25955,21 +25955,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -25979,10 +25979,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>407153</v>
+        <v>407400</v>
       </c>
       <c r="R260" t="n">
-        <v>6823235</v>
+        <v>6822547</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26041,10 +26041,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>129495301</v>
+        <v>129495328</v>
       </c>
       <c r="B261" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26052,21 +26052,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26076,10 +26076,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>407337</v>
+        <v>407113</v>
       </c>
       <c r="R261" t="n">
-        <v>6822261</v>
+        <v>6823088</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26138,10 +26138,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>129495351</v>
+        <v>129495299</v>
       </c>
       <c r="B262" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26149,21 +26149,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26173,10 +26173,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>407400</v>
+        <v>407363</v>
       </c>
       <c r="R262" t="n">
-        <v>6822547</v>
+        <v>6822174</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -26235,10 +26235,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>129495328</v>
+        <v>129495293</v>
       </c>
       <c r="B263" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26246,21 +26246,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -26270,10 +26270,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>407113</v>
+        <v>407453</v>
       </c>
       <c r="R263" t="n">
-        <v>6823088</v>
+        <v>6822397</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -26332,7 +26332,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>129495299</v>
+        <v>129495287</v>
       </c>
       <c r="B264" t="n">
         <v>78838</v>
@@ -26367,10 +26367,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>407363</v>
+        <v>407279</v>
       </c>
       <c r="R264" t="n">
-        <v>6822174</v>
+        <v>6823092</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -26429,10 +26429,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>129495293</v>
+        <v>129495238</v>
       </c>
       <c r="B265" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -26440,34 +26440,42 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>407453</v>
+        <v>407146</v>
       </c>
       <c r="R265" t="n">
-        <v>6822397</v>
+        <v>6823277</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -26526,10 +26534,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>129495287</v>
+        <v>129495246</v>
       </c>
       <c r="B266" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -26537,34 +26545,42 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>407279</v>
+        <v>407293</v>
       </c>
       <c r="R266" t="n">
-        <v>6823092</v>
+        <v>6822570</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -26623,10 +26639,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>129495238</v>
+        <v>129478245</v>
       </c>
       <c r="B267" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -26634,42 +26650,34 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>407146</v>
+        <v>407208</v>
       </c>
       <c r="R267" t="n">
-        <v>6823277</v>
+        <v>6823030</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -26716,22 +26724,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>129495246</v>
+        <v>129495253</v>
       </c>
       <c r="B268" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -26739,42 +26747,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>407293</v>
+        <v>407153</v>
       </c>
       <c r="R268" t="n">
-        <v>6822570</v>
+        <v>6823235</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>

--- a/artfynd/A 44936-2025 artfynd.xlsx
+++ b/artfynd/A 44936-2025 artfynd.xlsx
@@ -2142,10 +2142,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495244</v>
+        <v>129495213</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2153,42 +2153,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407468</v>
+        <v>407299</v>
       </c>
       <c r="R17" t="n">
-        <v>6822379</v>
+        <v>6822574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2538,10 +2530,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129495213</v>
+        <v>129495244</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,34 +2541,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407299</v>
+        <v>407468</v>
       </c>
       <c r="R21" t="n">
-        <v>6822574</v>
+        <v>6822379</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129495291</v>
+        <v>129478260</v>
       </c>
       <c r="B51" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5499,21 +5499,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>407457</v>
+        <v>407390</v>
       </c>
       <c r="R51" t="n">
-        <v>6822425</v>
+        <v>6822446</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5573,22 +5573,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129478300</v>
+        <v>129495228</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5596,21 +5596,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>407468</v>
+        <v>407368</v>
       </c>
       <c r="R52" t="n">
-        <v>6822633</v>
+        <v>6822481</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5670,22 +5670,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129495285</v>
+        <v>129478262</v>
       </c>
       <c r="B53" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5693,21 +5693,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5717,10 +5717,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>407222</v>
+        <v>407384</v>
       </c>
       <c r="R53" t="n">
-        <v>6823145</v>
+        <v>6822532</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5767,22 +5767,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129495194</v>
+        <v>129495291</v>
       </c>
       <c r="B54" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5790,21 +5790,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>407452</v>
+        <v>407457</v>
       </c>
       <c r="R54" t="n">
-        <v>6822376</v>
+        <v>6822425</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5876,10 +5876,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129495286</v>
+        <v>129478300</v>
       </c>
       <c r="B55" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5887,21 +5887,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>407274</v>
+        <v>407468</v>
       </c>
       <c r="R55" t="n">
-        <v>6823142</v>
+        <v>6822633</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5961,22 +5961,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129478302</v>
+        <v>129495285</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5984,21 +5984,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>407408</v>
+        <v>407222</v>
       </c>
       <c r="R56" t="n">
-        <v>6822212</v>
+        <v>6823145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6058,22 +6058,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129478281</v>
+        <v>129495194</v>
       </c>
       <c r="B57" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>407417</v>
+        <v>407452</v>
       </c>
       <c r="R57" t="n">
-        <v>6822269</v>
+        <v>6822376</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6155,22 +6155,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129478298</v>
+        <v>129495286</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6178,21 +6178,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6202,10 +6202,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>407339</v>
+        <v>407274</v>
       </c>
       <c r="R58" t="n">
-        <v>6822779</v>
+        <v>6823142</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6240,11 +6240,6 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6257,22 +6252,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129495308</v>
+        <v>129478302</v>
       </c>
       <c r="B59" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6280,21 +6275,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6304,10 +6299,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>407326</v>
+        <v>407408</v>
       </c>
       <c r="R59" t="n">
-        <v>6822521</v>
+        <v>6822212</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6354,22 +6349,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129478305</v>
+        <v>129478281</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6377,21 +6372,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6401,10 +6396,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>407395</v>
+        <v>407417</v>
       </c>
       <c r="R60" t="n">
-        <v>6822461</v>
+        <v>6822269</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6463,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129495233</v>
+        <v>129478298</v>
       </c>
       <c r="B61" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6474,42 +6469,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>407317</v>
+        <v>407339</v>
       </c>
       <c r="R61" t="n">
-        <v>6822622</v>
+        <v>6822779</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6544,6 +6531,11 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6556,22 +6548,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129478260</v>
+        <v>129495308</v>
       </c>
       <c r="B62" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6579,21 +6571,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6603,10 +6595,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>407390</v>
+        <v>407326</v>
       </c>
       <c r="R62" t="n">
-        <v>6822446</v>
+        <v>6822521</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6653,22 +6645,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129495228</v>
+        <v>129478305</v>
       </c>
       <c r="B63" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6676,21 +6668,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6700,10 +6692,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>407368</v>
+        <v>407395</v>
       </c>
       <c r="R63" t="n">
-        <v>6822481</v>
+        <v>6822461</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6750,22 +6742,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129478262</v>
+        <v>129495233</v>
       </c>
       <c r="B64" t="n">
-        <v>78839</v>
+        <v>57896</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6773,34 +6765,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>407384</v>
+        <v>407317</v>
       </c>
       <c r="R64" t="n">
-        <v>6822532</v>
+        <v>6822622</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6847,22 +6847,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129495345</v>
+        <v>129495200</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6870,21 +6870,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>407343</v>
+        <v>407347</v>
       </c>
       <c r="R65" t="n">
-        <v>6822692</v>
+        <v>6822264</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129495203</v>
+        <v>129478218</v>
       </c>
       <c r="B66" t="n">
         <v>79700</v>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>407358</v>
+        <v>407429</v>
       </c>
       <c r="R66" t="n">
-        <v>6822335</v>
+        <v>6822365</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7041,19 +7041,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129478230</v>
+        <v>129495197</v>
       </c>
       <c r="B67" t="n">
         <v>79700</v>
@@ -7088,10 +7088,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>407287</v>
+        <v>407464</v>
       </c>
       <c r="R67" t="n">
-        <v>6822652</v>
+        <v>6822325</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7138,22 +7138,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129495290</v>
+        <v>129495345</v>
       </c>
       <c r="B68" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7161,21 +7161,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>407458</v>
+        <v>407343</v>
       </c>
       <c r="R68" t="n">
-        <v>6822444</v>
+        <v>6822692</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7247,10 +7247,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129478270</v>
+        <v>129495203</v>
       </c>
       <c r="B69" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>407243</v>
+        <v>407358</v>
       </c>
       <c r="R69" t="n">
-        <v>6823199</v>
+        <v>6822335</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7332,22 +7332,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129495360</v>
+        <v>129478230</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7355,21 +7355,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>407376</v>
+        <v>407287</v>
       </c>
       <c r="R70" t="n">
-        <v>6822395</v>
+        <v>6822652</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7429,22 +7429,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129495214</v>
+        <v>129495290</v>
       </c>
       <c r="B71" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7452,21 +7452,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>407299</v>
+        <v>407458</v>
       </c>
       <c r="R71" t="n">
-        <v>6822612</v>
+        <v>6822444</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7538,10 +7538,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129495190</v>
+        <v>129478270</v>
       </c>
       <c r="B72" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7549,21 +7549,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>407458</v>
+        <v>407243</v>
       </c>
       <c r="R72" t="n">
-        <v>6822443</v>
+        <v>6823199</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7623,22 +7623,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129478211</v>
+        <v>129495360</v>
       </c>
       <c r="B73" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7646,21 +7646,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>407537</v>
+        <v>407376</v>
       </c>
       <c r="R73" t="n">
-        <v>6822377</v>
+        <v>6822395</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7720,22 +7720,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129495347</v>
+        <v>129495214</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7743,21 +7743,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>407351</v>
+        <v>407299</v>
       </c>
       <c r="R74" t="n">
-        <v>6822654</v>
+        <v>6822612</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7829,7 +7829,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129478226</v>
+        <v>129495190</v>
       </c>
       <c r="B75" t="n">
         <v>79700</v>
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>407364</v>
+        <v>407458</v>
       </c>
       <c r="R75" t="n">
-        <v>6822528</v>
+        <v>6822443</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7914,22 +7914,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129495313</v>
+        <v>129478211</v>
       </c>
       <c r="B76" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7937,21 +7937,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7961,10 +7961,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>407306</v>
+        <v>407537</v>
       </c>
       <c r="R76" t="n">
-        <v>6822621</v>
+        <v>6822377</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8011,19 +8011,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129495346</v>
+        <v>129495347</v>
       </c>
       <c r="B77" t="n">
         <v>79081</v>
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>407368</v>
+        <v>407351</v>
       </c>
       <c r="R77" t="n">
-        <v>6822673</v>
+        <v>6822654</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8120,10 +8120,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129495292</v>
+        <v>129478226</v>
       </c>
       <c r="B78" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8131,21 +8131,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>407489</v>
+        <v>407364</v>
       </c>
       <c r="R78" t="n">
-        <v>6822422</v>
+        <v>6822528</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8205,22 +8205,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129495179</v>
+        <v>129495313</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8228,21 +8228,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8252,10 +8252,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>407142</v>
+        <v>407306</v>
       </c>
       <c r="R79" t="n">
-        <v>6823410</v>
+        <v>6822621</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8314,10 +8314,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129495192</v>
+        <v>129495346</v>
       </c>
       <c r="B80" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8325,21 +8325,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>407490</v>
+        <v>407368</v>
       </c>
       <c r="R80" t="n">
-        <v>6822426</v>
+        <v>6822673</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129495167</v>
+        <v>129495292</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8422,21 +8422,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8446,10 +8446,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>407179</v>
+        <v>407489</v>
       </c>
       <c r="R81" t="n">
-        <v>6822946</v>
+        <v>6822422</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129495200</v>
+        <v>129495179</v>
       </c>
       <c r="B82" t="n">
         <v>79700</v>
@@ -8543,10 +8543,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>407347</v>
+        <v>407142</v>
       </c>
       <c r="R82" t="n">
-        <v>6822264</v>
+        <v>6823410</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8605,7 +8605,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129478218</v>
+        <v>129495192</v>
       </c>
       <c r="B83" t="n">
         <v>79700</v>
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>407429</v>
+        <v>407490</v>
       </c>
       <c r="R83" t="n">
-        <v>6822365</v>
+        <v>6822426</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8690,19 +8690,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129495197</v>
+        <v>129495167</v>
       </c>
       <c r="B84" t="n">
         <v>79700</v>
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>407464</v>
+        <v>407179</v>
       </c>
       <c r="R84" t="n">
-        <v>6822325</v>
+        <v>6822946</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -14181,10 +14181,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129478241</v>
+        <v>129495274</v>
       </c>
       <c r="B140" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14192,42 +14192,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>407386</v>
+        <v>407307</v>
       </c>
       <c r="R140" t="n">
-        <v>6822497</v>
+        <v>6822633</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14274,22 +14266,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129478242</v>
+        <v>129495260</v>
       </c>
       <c r="B141" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14297,42 +14289,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>407332</v>
+        <v>407407</v>
       </c>
       <c r="R141" t="n">
-        <v>6822601</v>
+        <v>6822570</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14367,11 +14351,6 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Samt läte</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -14384,19 +14363,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129495274</v>
+        <v>129495252</v>
       </c>
       <c r="B142" t="n">
         <v>78839</v>
@@ -14431,10 +14410,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>407307</v>
+        <v>407196</v>
       </c>
       <c r="R142" t="n">
-        <v>6822633</v>
+        <v>6823280</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14493,10 +14472,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129495260</v>
+        <v>129478241</v>
       </c>
       <c r="B143" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14504,34 +14483,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>407407</v>
+        <v>407386</v>
       </c>
       <c r="R143" t="n">
-        <v>6822570</v>
+        <v>6822497</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14578,22 +14565,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129495252</v>
+        <v>129478242</v>
       </c>
       <c r="B144" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14601,34 +14588,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>407196</v>
+        <v>407332</v>
       </c>
       <c r="R144" t="n">
-        <v>6823280</v>
+        <v>6822601</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14663,6 +14658,11 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Samt läte</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
@@ -14675,12 +14675,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -15560,10 +15560,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129495344</v>
+        <v>129495239</v>
       </c>
       <c r="B154" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15571,34 +15571,42 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>407329</v>
+        <v>407133</v>
       </c>
       <c r="R154" t="n">
-        <v>6822724</v>
+        <v>6823278</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15657,10 +15665,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129478231</v>
+        <v>129495237</v>
       </c>
       <c r="B155" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15668,34 +15676,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>407270</v>
+        <v>407194</v>
       </c>
       <c r="R155" t="n">
-        <v>6822722</v>
+        <v>6823308</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15742,22 +15758,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129478271</v>
+        <v>129478251</v>
       </c>
       <c r="B156" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15765,21 +15781,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15789,10 +15805,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>407272</v>
+        <v>407266</v>
       </c>
       <c r="R156" t="n">
-        <v>6823147</v>
+        <v>6823123</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15851,10 +15867,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129495337</v>
+        <v>129495225</v>
       </c>
       <c r="B157" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15862,21 +15878,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -15886,10 +15902,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>407281</v>
+        <v>407359</v>
       </c>
       <c r="R157" t="n">
-        <v>6822996</v>
+        <v>6822322</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -15948,10 +15964,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129478228</v>
+        <v>129495229</v>
       </c>
       <c r="B158" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15959,21 +15975,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -15983,10 +15999,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>407325</v>
+        <v>407299</v>
       </c>
       <c r="R158" t="n">
-        <v>6822646</v>
+        <v>6822612</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16033,22 +16049,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129478217</v>
+        <v>129495344</v>
       </c>
       <c r="B159" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16056,21 +16072,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16080,10 +16096,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>407385</v>
+        <v>407329</v>
       </c>
       <c r="R159" t="n">
-        <v>6822314</v>
+        <v>6822724</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16130,22 +16146,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129495312</v>
+        <v>129478231</v>
       </c>
       <c r="B160" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16153,21 +16169,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16177,10 +16193,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>407301</v>
+        <v>407270</v>
       </c>
       <c r="R160" t="n">
-        <v>6822575</v>
+        <v>6822722</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16227,22 +16243,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129495202</v>
+        <v>129478271</v>
       </c>
       <c r="B161" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16250,21 +16266,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16274,10 +16290,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>407355</v>
+        <v>407272</v>
       </c>
       <c r="R161" t="n">
-        <v>6822321</v>
+        <v>6823147</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16324,22 +16340,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129478227</v>
+        <v>129495337</v>
       </c>
       <c r="B162" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16347,21 +16363,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16371,10 +16387,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>407333</v>
+        <v>407281</v>
       </c>
       <c r="R162" t="n">
-        <v>6822601</v>
+        <v>6822996</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16421,19 +16437,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129478220</v>
+        <v>129478228</v>
       </c>
       <c r="B163" t="n">
         <v>79700</v>
@@ -16468,10 +16484,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>407390</v>
+        <v>407325</v>
       </c>
       <c r="R163" t="n">
-        <v>6822450</v>
+        <v>6822646</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16530,7 +16546,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129495174</v>
+        <v>129478217</v>
       </c>
       <c r="B164" t="n">
         <v>79700</v>
@@ -16565,10 +16581,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>407052</v>
+        <v>407385</v>
       </c>
       <c r="R164" t="n">
-        <v>6823345</v>
+        <v>6822314</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16615,22 +16631,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129478204</v>
+        <v>129495312</v>
       </c>
       <c r="B165" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16638,21 +16654,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -16662,10 +16678,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>407300</v>
+        <v>407301</v>
       </c>
       <c r="R165" t="n">
-        <v>6823030</v>
+        <v>6822575</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -16712,22 +16728,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129495239</v>
+        <v>129495202</v>
       </c>
       <c r="B166" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16735,42 +16751,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>407133</v>
+        <v>407355</v>
       </c>
       <c r="R166" t="n">
-        <v>6823278</v>
+        <v>6822321</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -16829,10 +16837,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129495237</v>
+        <v>129478227</v>
       </c>
       <c r="B167" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16840,42 +16848,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>407194</v>
+        <v>407333</v>
       </c>
       <c r="R167" t="n">
-        <v>6823308</v>
+        <v>6822601</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -16922,22 +16922,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129478251</v>
+        <v>129478220</v>
       </c>
       <c r="B168" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16945,21 +16945,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16969,10 +16969,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>407266</v>
+        <v>407390</v>
       </c>
       <c r="R168" t="n">
-        <v>6823123</v>
+        <v>6822450</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17031,10 +17031,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129495225</v>
+        <v>129495174</v>
       </c>
       <c r="B169" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17042,21 +17042,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17066,10 +17066,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>407359</v>
+        <v>407052</v>
       </c>
       <c r="R169" t="n">
-        <v>6822322</v>
+        <v>6823345</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17128,10 +17128,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129495229</v>
+        <v>129478204</v>
       </c>
       <c r="B170" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17139,21 +17139,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17163,10 +17163,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>407299</v>
+        <v>407300</v>
       </c>
       <c r="R170" t="n">
-        <v>6822612</v>
+        <v>6823030</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17213,12 +17213,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>

--- a/artfynd/A 44936-2025 artfynd.xlsx
+++ b/artfynd/A 44936-2025 artfynd.xlsx
@@ -21056,10 +21056,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129478224</v>
+        <v>129495270</v>
       </c>
       <c r="B210" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21067,21 +21067,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21091,10 +21091,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>407365</v>
+        <v>407342</v>
       </c>
       <c r="R210" t="n">
-        <v>6822523</v>
+        <v>6822388</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21141,22 +21141,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129495277</v>
+        <v>129495220</v>
       </c>
       <c r="B211" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21164,21 +21164,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21188,10 +21188,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>407182</v>
+        <v>407451</v>
       </c>
       <c r="R211" t="n">
-        <v>6823012</v>
+        <v>6822425</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21250,7 +21250,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129495181</v>
+        <v>129478224</v>
       </c>
       <c r="B212" t="n">
         <v>79700</v>
@@ -21285,10 +21285,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>407197</v>
+        <v>407365</v>
       </c>
       <c r="R212" t="n">
-        <v>6823283</v>
+        <v>6822523</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21335,19 +21335,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129495304</v>
+        <v>129495277</v>
       </c>
       <c r="B213" t="n">
         <v>78838</v>
@@ -21382,10 +21382,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>407342</v>
+        <v>407182</v>
       </c>
       <c r="R213" t="n">
-        <v>6822388</v>
+        <v>6823012</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21444,7 +21444,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129495171</v>
+        <v>129495181</v>
       </c>
       <c r="B214" t="n">
         <v>79700</v>
@@ -21479,10 +21479,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>407073</v>
+        <v>407197</v>
       </c>
       <c r="R214" t="n">
-        <v>6823197</v>
+        <v>6823283</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21541,10 +21541,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129495364</v>
+        <v>129495304</v>
       </c>
       <c r="B215" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21552,37 +21552,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>407373</v>
+        <v>407342</v>
       </c>
       <c r="R215" t="n">
-        <v>6822509</v>
+        <v>6822388</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21623,7 +21620,6 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
-      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -21642,10 +21638,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129495296</v>
+        <v>129495171</v>
       </c>
       <c r="B216" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21653,21 +21649,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -21677,10 +21673,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>407469</v>
+        <v>407073</v>
       </c>
       <c r="R216" t="n">
-        <v>6822344</v>
+        <v>6823197</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -21739,10 +21735,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129478206</v>
+        <v>129495364</v>
       </c>
       <c r="B217" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21750,34 +21746,37 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>407513</v>
+        <v>407373</v>
       </c>
       <c r="R217" t="n">
-        <v>6822490</v>
+        <v>6822509</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -21818,28 +21817,29 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
+      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129495353</v>
+        <v>129495296</v>
       </c>
       <c r="B218" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21847,21 +21847,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -21871,10 +21871,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>407394</v>
+        <v>407469</v>
       </c>
       <c r="R218" t="n">
-        <v>6822495</v>
+        <v>6822344</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129495310</v>
+        <v>129478206</v>
       </c>
       <c r="B219" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21944,37 +21944,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>407318</v>
+        <v>407513</v>
       </c>
       <c r="R219" t="n">
-        <v>6822539</v>
+        <v>6822490</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22015,29 +22012,28 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129495211</v>
+        <v>129495353</v>
       </c>
       <c r="B220" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22045,21 +22041,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22069,10 +22065,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>407312</v>
+        <v>407394</v>
       </c>
       <c r="R220" t="n">
-        <v>6822520</v>
+        <v>6822495</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22131,7 +22127,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129495306</v>
+        <v>129495310</v>
       </c>
       <c r="B221" t="n">
         <v>78838</v>
@@ -22160,16 +22156,19 @@
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Uppbladsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>407349</v>
+        <v>407318</v>
       </c>
       <c r="R221" t="n">
-        <v>6822438</v>
+        <v>6822539</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22210,6 +22209,7 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -22228,10 +22228,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129478277</v>
+        <v>129495211</v>
       </c>
       <c r="B222" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22239,21 +22239,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22263,10 +22263,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>407513</v>
+        <v>407312</v>
       </c>
       <c r="R222" t="n">
-        <v>6822486</v>
+        <v>6822520</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22313,19 +22313,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129478282</v>
+        <v>129495306</v>
       </c>
       <c r="B223" t="n">
         <v>78838</v>
@@ -22360,10 +22360,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>407415</v>
+        <v>407349</v>
       </c>
       <c r="R223" t="n">
-        <v>6822315</v>
+        <v>6822438</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22410,22 +22410,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129495270</v>
+        <v>129478277</v>
       </c>
       <c r="B224" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22433,21 +22433,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -22457,10 +22457,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>407342</v>
+        <v>407513</v>
       </c>
       <c r="R224" t="n">
-        <v>6822388</v>
+        <v>6822486</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22507,22 +22507,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129495220</v>
+        <v>129478282</v>
       </c>
       <c r="B225" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22530,21 +22530,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22554,10 +22554,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>407451</v>
+        <v>407415</v>
       </c>
       <c r="R225" t="n">
-        <v>6822425</v>
+        <v>6822315</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22604,12 +22604,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>

--- a/artfynd/A 44936-2025 artfynd.xlsx
+++ b/artfynd/A 44936-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY289"/>
+  <dimension ref="A1:AZ289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478236</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495320</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478238</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478239</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478294</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478295</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478296</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478297</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478298</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478299</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1768,6 +1823,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478300</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478301</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1962,6 +2027,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478302</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2059,6 +2129,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478303</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2156,6 +2231,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478304</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2253,6 +2333,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478305</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478306</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2457,6 +2547,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478307</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2554,6 +2649,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478308</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2660,6 +2760,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495321</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2757,6 +2862,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495322</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2854,6 +2964,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495323</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2951,6 +3066,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495324</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3048,6 +3168,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495325</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3145,6 +3270,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495326</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3242,6 +3372,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495328</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3339,6 +3474,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495329</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3436,6 +3576,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495330</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3533,6 +3678,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495331</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3630,6 +3780,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495332</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3727,6 +3882,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495333</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3824,6 +3984,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495334</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3921,6 +4086,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495335</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4018,6 +4188,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495336</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4115,6 +4290,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495337</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4221,6 +4401,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495338</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4318,6 +4503,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495339</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4424,6 +4614,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495340</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4521,6 +4716,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495341</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4618,6 +4818,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495342</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4724,6 +4929,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495343</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4821,6 +5031,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495344</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4918,6 +5133,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495345</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5015,6 +5235,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495346</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5112,6 +5337,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495347</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5213,6 +5443,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495348</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5310,6 +5545,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495349</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5411,6 +5651,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495350</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5508,6 +5753,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495351</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5605,6 +5855,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495352</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5702,6 +5957,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495353</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5799,6 +6059,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495354</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5896,6 +6161,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495355</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5993,6 +6263,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495356</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6094,6 +6369,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495357</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6191,6 +6471,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495358</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6292,6 +6577,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495359</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6389,6 +6679,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495360</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6486,6 +6781,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495361</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6583,6 +6883,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495363</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6684,6 +6989,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495364</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6785,6 +7095,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495365</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6882,6 +7197,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495366</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6979,6 +7299,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495367</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7076,6 +7401,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495368</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7173,6 +7503,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495369</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7270,6 +7605,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495370</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7367,6 +7707,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495371</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7464,6 +7809,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478264</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7561,6 +7911,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478265</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7658,6 +8013,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478266</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7755,6 +8115,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478267</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7852,6 +8217,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478268</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7949,6 +8319,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478269</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8046,6 +8421,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478270</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8143,6 +8523,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478271</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8240,6 +8625,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478272</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8337,6 +8727,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478273</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8434,6 +8829,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478274</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8531,6 +8931,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478275</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8628,6 +9033,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478276</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8725,6 +9135,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478277</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8822,6 +9237,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478278</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8919,6 +9339,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478279</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9016,6 +9441,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478280</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9113,6 +9543,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478281</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9210,6 +9645,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478282</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9307,6 +9747,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478283</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9404,6 +9849,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478284</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9501,6 +9951,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478285</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9598,6 +10053,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478286</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9695,6 +10155,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478287</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9792,6 +10257,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495276</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9889,6 +10359,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495277</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9986,6 +10461,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495278</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10083,6 +10563,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495279</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10180,6 +10665,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495280</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10277,6 +10767,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495282</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10374,6 +10869,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495284</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10471,6 +10971,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495285</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10568,6 +11073,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495286</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10665,6 +11175,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495287</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10762,6 +11277,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495288</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10864,6 +11384,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495289</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10961,6 +11486,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495290</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11058,6 +11588,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495291</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11155,6 +11690,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495292</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11252,6 +11792,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495293</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11349,6 +11894,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495294</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11446,6 +11996,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495296</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11543,6 +12098,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495297</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11640,6 +12200,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495298</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11737,6 +12302,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495299</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11834,6 +12404,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495300</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11931,6 +12506,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495301</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12028,6 +12608,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495302</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12125,6 +12710,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495304</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12222,6 +12812,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495305</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12319,6 +12914,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495306</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12420,6 +13020,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495307</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12517,6 +13122,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495308</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12614,6 +13224,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495309</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12715,6 +13330,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495310</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12816,6 +13436,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495311</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12913,6 +13538,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495312</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13010,6 +13640,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495313</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13107,6 +13742,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495314</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13204,6 +13844,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495316</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13301,6 +13946,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495317</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13398,6 +14048,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478200</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13495,6 +14150,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478201</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13592,6 +14252,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478202</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13689,6 +14354,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478203</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13786,6 +14456,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478204</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13883,6 +14558,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478205</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13980,6 +14660,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478206</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14077,6 +14762,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478207</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14174,6 +14864,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478208</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14271,6 +14966,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478209</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14368,6 +15068,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478210</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14465,6 +15170,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478211</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14562,6 +15272,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478212</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14659,6 +15374,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478213</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14756,6 +15476,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478214</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14853,6 +15578,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478215</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14950,6 +15680,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478216</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15047,6 +15782,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478217</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15144,6 +15884,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478218</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15241,6 +15986,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478219</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15338,6 +16088,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478220</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15435,6 +16190,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478221</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15532,6 +16292,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478222</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15629,6 +16394,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478223</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15726,6 +16496,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478224</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15823,6 +16598,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478226</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15920,6 +16700,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478227</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16017,6 +16802,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478228</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16114,6 +16904,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478229</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16211,6 +17006,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478230</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16308,6 +17108,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478231</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16405,6 +17210,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478232</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16502,6 +17312,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495167</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16599,6 +17414,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495168</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16696,6 +17516,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495169</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16793,6 +17618,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495170</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16890,6 +17720,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495171</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -16987,6 +17822,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495172</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17084,6 +17924,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495173</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17181,6 +18026,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495174</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17278,6 +18128,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495175</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17375,6 +18230,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495176</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17472,6 +18332,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495177</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17569,6 +18434,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495178</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17666,6 +18536,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495179</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17763,6 +18638,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495180</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -17860,6 +18740,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495181</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -17957,6 +18842,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495182</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18054,6 +18944,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495183</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18151,6 +19046,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495184</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18248,6 +19148,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495185</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18345,6 +19250,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495186</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18442,6 +19352,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495187</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18539,6 +19454,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495188</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18636,6 +19556,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495189</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18733,6 +19658,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495190</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -18830,6 +19760,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495191</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -18927,6 +19862,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495192</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19024,6 +19964,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495193</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19121,6 +20066,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495194</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19218,6 +20168,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495195</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19315,6 +20270,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495196</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19412,6 +20372,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495197</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19509,6 +20474,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495198</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19606,6 +20576,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495199</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19703,6 +20678,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495200</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -19800,6 +20780,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495201</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -19897,6 +20882,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495202</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -19994,6 +20984,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495203</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20091,6 +21086,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495204</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20188,6 +21188,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495205</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20285,6 +21290,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495206</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20382,6 +21392,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495207</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20479,6 +21494,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495208</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20576,6 +21596,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495209</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20673,6 +21698,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495210</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -20770,6 +21800,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495211</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -20867,6 +21902,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495212</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -20964,6 +22004,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495213</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21061,6 +22106,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495214</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21158,6 +22208,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495215</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21263,6 +22318,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478240</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21368,6 +22428,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478241</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21478,6 +22543,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478242</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21583,6 +22653,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495236</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21688,6 +22763,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495237</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -21793,6 +22873,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495238</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -21898,6 +22983,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495239</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22003,6 +23093,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495240</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22108,6 +23203,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495241</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22213,6 +23313,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495242</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22318,6 +23423,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495243</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22423,6 +23533,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495244</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22528,6 +23643,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495245</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22633,6 +23753,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495246</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -22739,6 +23864,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478237</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -22844,6 +23974,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495230</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -22949,6 +24084,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495231</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23054,6 +24194,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495232</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23159,6 +24304,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495275</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23264,6 +24414,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495233</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23361,6 +24516,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478245</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23458,6 +24618,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478246</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23555,6 +24720,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478247</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23652,6 +24822,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478248</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23749,6 +24924,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478249</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -23846,6 +25026,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478250</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -23943,6 +25128,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478251</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24040,6 +25230,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478252</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24137,6 +25332,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478253</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24234,6 +25434,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478254</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24331,6 +25536,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478255</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24428,6 +25638,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478256</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24525,6 +25740,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478257</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24622,6 +25842,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478258</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -24719,6 +25944,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478259</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -24816,6 +26046,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478260</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -24913,6 +26148,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478261</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25010,6 +26250,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478262</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25107,6 +26352,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495248</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25204,6 +26454,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495249</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25301,6 +26556,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495250</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25398,6 +26658,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495251</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25495,6 +26760,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495252</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25592,6 +26862,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495253</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -25689,6 +26964,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495254</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -25786,6 +27066,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495255</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -25887,6 +27172,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495256</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -25984,6 +27274,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495258</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26081,6 +27376,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495259</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26178,6 +27478,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495260</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26275,6 +27580,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495261</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26372,6 +27682,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495262</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26469,6 +27784,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495263</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -26566,6 +27886,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495264</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -26667,6 +27992,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495265</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -26764,6 +28094,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495266</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -26861,6 +28196,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495267</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -26958,6 +28298,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495268</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27055,6 +28400,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495269</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27152,6 +28502,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495270</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27249,6 +28604,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495271</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -27346,6 +28706,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495272</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -27443,6 +28808,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495273</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -27540,6 +28910,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495274</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -27638,6 +29013,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478233</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -27736,6 +29116,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478234</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -27834,6 +29219,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129478235</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -27931,6 +29321,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495216</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28028,6 +29423,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495217</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28125,6 +29525,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495218</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28226,6 +29631,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495219</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -28323,6 +29733,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495220</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -28420,6 +29835,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495222</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -28517,6 +29937,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495224</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -28614,6 +30039,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495225</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -28711,6 +30141,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495226</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -28808,6 +30243,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495228</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -28905,8 +30345,303 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129495229</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>